--- a/order_generation/PO_excel_export/factory-5.xlsx
+++ b/order_generation/PO_excel_export/factory-5.xlsx
@@ -350,7 +350,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1581150" cy="1266825"/>
+    <ext cx="1266825" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -761,7 +761,7 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>盐城市艳丽工艺品有限公司</t>
+          <t>宁波市海曙硕丰塑料五金制品有限公司</t>
         </is>
       </c>
       <c r="C3" s="16" t="n"/>
@@ -787,7 +787,7 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>0574-27889688</t>
+          <t>电话: +86-574-27889688   传真: +86-574-27889677</t>
         </is>
       </c>
       <c r="C4" s="16" t="n"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>XX印刷厂</t>
+          <t>小张</t>
         </is>
       </c>
       <c r="C5" s="16" t="n"/>
@@ -826,7 +826,7 @@
       </c>
       <c r="G5" s="18" t="inlineStr">
         <is>
-          <t>郑遥杰</t>
+          <t>孙诚昱</t>
         </is>
       </c>
       <c r="H5" s="16" t="n"/>
@@ -872,30 +872,44 @@
     <row r="7" ht="100" customFormat="1" customHeight="1" s="2">
       <c r="A7" s="29" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>ST1122-1</t>
         </is>
       </c>
       <c r="B7" s="29" t="n"/>
       <c r="C7" s="29" t="inlineStr">
         <is>
-          <t>15*20黑色棘皮绒单面，黑色棉绳，双色logo，N字母烫金</t>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+            </rPr>
+            <t>黑色气垫猪鬃手柄：水曲柳手柄棕黑色喷漆双层，喷漆效果参考Moroccooil，形状同寄样。8.5*24.5*1.3，金色移印logoNorsewood。梳面开口严格按照提供线稿，礼盒包装我司提供，</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FFFFFF"/>
+            </rPr>
+            <t>胶皮配件我司提供</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00FFFFFF"/>
+            </rPr>
+            <t>，清洁刷和布袋我司提供，需装配，贴标。</t>
+          </r>
         </is>
       </c>
       <c r="D7" s="29" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>1.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F7" s="29">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="29" t="inlineStr">
-        <is>
-          <t>散货</t>
-        </is>
-      </c>
+      <c r="G7" s="29" t="inlineStr"/>
       <c r="H7" s="20" t="n"/>
     </row>
     <row r="8" ht="100.15" customFormat="1" customHeight="1" s="2">
@@ -956,7 +970,7 @@
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>浙江省 宁波市海曙区高桥镇秀丰路67号1栋2楼，小张 18668289261</t>
+          <t>宁波市海曙区高桥镇秀丰路67号1栋1楼，小张，18668289261</t>
         </is>
       </c>
       <c r="C12" s="25" t="n"/>
@@ -974,7 +988,7 @@
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>款到发货</t>
+          <t>含税含运含进仓</t>
         </is>
       </c>
       <c r="C13" s="25" t="n"/>
@@ -1000,7 +1014,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>15天</t>
+          <t>45天</t>
         </is>
       </c>
       <c r="C14" s="25" t="n"/>
@@ -1067,7 +1081,16 @@
       <c r="H18" s="25" t="n"/>
     </row>
     <row r="19" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A19" s="25" t="inlineStr"/>
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>双层漆效果参考以寄样为准，
+配件需要全部入纸袋然后放进礼盒包装，
+双层漆效果参考以寄样为准，
+木柄表面处理平整干净，没有坑洼， 气垫与木柄交接处，没有缝隙
+配件需要全部入纸袋然后放进礼盒包装，
+气垫梳60/箱 80箱</t>
+        </is>
+      </c>
       <c r="B19" s="25" t="n"/>
       <c r="C19" s="25" t="n"/>
       <c r="D19" s="25" t="n"/>
@@ -1342,7 +1365,7 @@
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>盐城市艳丽工艺品有限公司</t>
+          <t>宁波市海曙硕丰塑料五金制品有限公司</t>
         </is>
       </c>
       <c r="F69" s="9" t="n"/>
